--- a/mentors.xlsx
+++ b/mentors.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wadhwanifoundation-my.sharepoint.com/personal/meenakshi_singh_wadhwanifoundation_org/Documents/04. Advisors/2026/Test AI Mentor Search/MentorSearchAI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_F25DC773A252ABDACC104819499C5E4E5BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9129EC1-7E81-4A4A-998F-FF8E11F078FE}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_F25DC773A252ABDACC104819499C5E4E5BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBF2DD90-0550-496F-8F76-FC7CEC9E174C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="46">
   <si>
     <t>Name</t>
   </si>
@@ -39,64 +50,238 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Raj Mehta</t>
-  </si>
-  <si>
-    <t>Fundraising, Pitching</t>
-  </si>
-  <si>
-    <t>Fintech</t>
-  </si>
-  <si>
-    <t>Helps startups raise funds and prepare investor decks</t>
-  </si>
-  <si>
-    <t>Neha Sharma</t>
-  </si>
-  <si>
-    <t>Marketing, Growth</t>
-  </si>
-  <si>
-    <t>D2C</t>
-  </si>
-  <si>
-    <t>Expert in digital marketing and customer acquisition</t>
-  </si>
-  <si>
-    <t>Amit Jain</t>
-  </si>
-  <si>
-    <t>Product, MVP</t>
-  </si>
-  <si>
-    <t>SaaS</t>
-  </si>
-  <si>
-    <t>Helps build MVP and scale product</t>
-  </si>
-  <si>
-    <t>Sneha Kapoor</t>
-  </si>
-  <si>
-    <t>HR, Hiring</t>
-  </si>
-  <si>
-    <t>Startups</t>
-  </si>
-  <si>
-    <t>Helps founders build strong teams</t>
-  </si>
-  <si>
-    <t>Vikram Singh</t>
-  </si>
-  <si>
-    <t>Sales, B2B</t>
-  </si>
-  <si>
-    <t>Enterprise</t>
-  </si>
-  <si>
-    <t>Expert in B2B sales and partnerships</t>
+    <t>Linkedin</t>
+  </si>
+  <si>
+    <t>Dr. Selva</t>
+  </si>
+  <si>
+    <t>Manish Sabnis</t>
+  </si>
+  <si>
+    <t>Mukul Agarwal2</t>
+  </si>
+  <si>
+    <t>Muthukumar Vemban</t>
+  </si>
+  <si>
+    <t>Pramod Harith R</t>
+  </si>
+  <si>
+    <t>Manik Koul</t>
+  </si>
+  <si>
+    <t>Dhruv Nath</t>
+  </si>
+  <si>
+    <t>Dr. Rakesh Malhotra</t>
+  </si>
+  <si>
+    <t>Simi Mishra</t>
+  </si>
+  <si>
+    <t>Ashish Jain</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/dr-selva-0849271b/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/manishsabnis2008/</t>
+  </si>
+  <si>
+    <t>https://linkedin.com/in/mukulag</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/muthukumarvemban/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/pramodharith/</t>
+  </si>
+  <si>
+    <t>http://linkedin.com/in/manik-koul/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/dhruvnathprof</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/dr-rakesh-malhotra-36713552/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/simi-mishra/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ashish-jain-1131283/</t>
+  </si>
+  <si>
+    <t>Dr. Selva is a senior Quality and Regulatory Affairs professional with 22 years of experience across medical devices, life sciences, biopharma, and AI-enabled healthcare products. He specializes in setting up greenfield manufacturing facilities, implementing compliant quality systems, and securing regulatory approvals across highly regulated global markets. 
+Core Expertise:
+Medical device quality and regulatory affairs, QMS implementation (ISO 13485, cGMP, 21 CFR Part 11), USFDA 510(k), EU MDR/IVDR, CE marking, SaMD and AI/ML-based medical devices, IVDs, clinical validations, technology transfer, and large-scale manufacturing operations. 
+Problem-Solving Approach:
+Adopts a structured, compliance-first approach that balances regulatory rigor with business practicality. Known for translating complex regulatory requirements into executable quality systems, he works closely with cross-functional teams to ensure timely approvals, operational efficiency, and cost optimization without compromising patient safety or compliance. 
+Impactful Projects:
+Led end-to-end quality and regulatory strategy for multiple medical devices, IVDs, and SaMD products, securing USFDA and CE approvals. Headed QARA functions at organizations such as SigTuple, Tech Mahindra, and Axio Biosolutions, enabling global market access and scalable manufacturing. Successfully commissioned greenfield facilities and managed large-scale stem cell and vaccine manufacturing operations across India and Malaysia. 
+Consultation Style:
+Hands-on, methodical, and collaborative. Works closely with leadership, R&amp;D, and manufacturing teams to build robust, audit-ready systems. Known for mentoring teams, driving capability building in regulatory compliance, and providing clear, actionable guidance tailored to product type, market, and organizational maturity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary:
+A seasoned business leader with multi-industry experience spanning over three decades, including two CEO roles across startup, scale-up, consolidation, and breakeven stages. Manish Sabnis has led large, complex organizations across retail, FMCG, OTC pharma, mobile phones, and food services, with deep expertise in both offline and digital B2C and B2B models. Currently serving as CEO at Grandiose Supermarkets (Ghassan Aboud Group) in the UAE, he brings together food retail, food service, and industrial production leadership. 
+Core Expertise:
+Retail and wholesale leadership, food and grocery retail, e-commerce and omnichannel business models, P&amp;L management, strategy and execution, supply chain and logistics, merchandising, private labels, organizational transformation, and large-scale team leadership. Strong exposure to FMCG, food services, bakery and catering operations, and technology-led retail platforms. 
+Problem-Solving Approach:
+Known for a structured, execution-focused approach that balances strategic clarity with operational discipline. Manish focuses on scaling technology- and supply-chain-intensive businesses, improving unit economics, and driving sustainable profitability through data-led decisions, organization redesign, and culture-building. He combines hands-on leadership with empowerment of high-performing teams. 
+Impactful Projects:
+Led the 7x scale-up of JioMart B2B grocery from INR 150 Cr to over INR 10,500 Cr, building a pan-India supply chain across 26 states and onboarding 1.5 million kirana and institutional customers. Played a key role in transforming METRO Cash &amp; Carry India through merchandising, private labels, and profitability improvements. As CEO of EasyDay, steered business expansion and integration during a major merger. Currently driving growth and differentiation at Grandiose Supermarkets, integrating premium retail, foodservice, bakery, catering, and digital channels. 
+Consultation Style:
+Direct, decisive, and highly collaborative. Engages closely with senior leadership while nurturing strong second-line teams. Known for inspirational leadership, clear accountability, and building cultures that encourage innovation, ownership, and sustained performance across large, diverse organizations. 
+</t>
+  </si>
+  <si>
+    <t>Summary
+A senior IT and digital transformation leader with over 20 years of experience across BFSI, NBFCs, and housing finance companies. Currently heading IT and Enterprise Applications, with a strong focus on building secure, scalable, and compliant technology ecosystems. Brings deep domain understanding of financial services combined with hands-on leadership in enterprise systems, cloud, cybersecurity, and regulatory technology.
+Core Expertise
+BFSI IT Leadership and Enterprise Applications
+Digital Transformation for NBFCs and HFCs
+Loan Origination Systems (LOS) and Loan Management Systems (LMS)
+Cloud Infrastructure and Cybersecurity
+IT Compliance aligned with RBI and NHB guidelines
+Fintech API and Credit Bureau Integrations
+IT Infrastructure Management and Active Directory
+Real-time MIS and Analytics Dashboards
+Problem-Solving Approach
+Takes a business-first approach to technology challenges by aligning IT strategy with regulatory needs, operational efficiency, and growth goals. Focuses on automating manual processes, modernizing legacy systems, strengthening security posture, and ensuring compliance without slowing business velocity. Known for practical execution and stakeholder alignment across business and tech teams.
+Impactful Projects
+Led enterprise-wide digital transformation across loan origination, servicing, collections, and compliance platforms
+Implemented LOS and LMS systems to improve turnaround time, reporting accuracy, and scalability
+Modernized cloud infrastructure and enforced cybersecurity frameworks across organizations
+Integrated fintech APIs and credit bureau services to strengthen underwriting and decision-making
+Built real-time dashboards enabling leadership teams to track performance and risk metrics
+Consultation Style
+Engages in a structured and collaborative manner, starting with a clear understanding of business priorities and regulatory constraints. Provides practical, implementation-focused guidance rather than theoretical advice. Adapts recommendations based on organizational maturity, risk appetite, and scale, ensuring solutions are both realistic and future-ready.</t>
+  </si>
+  <si>
+    <t>Summary:
+Muthukumar Vemban is a senior supply chain and operations leader with over three decades of experience across manufacturing, engineering, and end-to-end supply chain roles. Currently leading the Supply Chain Practice at Flipcarbon Integrated Solution, he focuses on scaling the practice rapidly while driving client acquisition, service delivery, pricing strategy, and portfolio design. His career spans large, complex organizations where he has consistently delivered cost, quality, and reliability improvements. 
+Core Expertise:
+Supply chain strategy, manufacturing operations, cost optimization, quality and reliability, Total Productive Maintenance (TPM), Six Sigma Black Belt execution, engineering leadership, sustainability in operations, budget control, and large-scale organizational capability building across FMCG, beverages, and industrial manufacturing. 
+Problem-Solving Approach:
+Takes a structured, data-led approach rooted in continuous improvement and cross-functional collaboration. Focuses on building fit-for-purpose organization structures, maturing sales and operations planning processes, and embedding cost discipline and operational excellence to deliver sustained bottom-line impact. 
+Impactful Projects:
+Led cost, quality, safety, and reliability transformations across multiple company-owned and contract manufacturing sites at SABMiller India, including end-to-end supply chain leadership for contract manufacturing. At Britannia Industries, drove performance across 13 owned manufacturing units. As Operations Director at Bacardi, strengthened manufacturing and supply chain outcomes. Earlier, delivered greenfield and brownfield plant projects at Coca-Cola India and EID Parry, contributing to ISO 9000 certification and large-scale operational upgrades. 
+Consultation Style:
+Pragmatic, hands-on, and outcome-oriented. Engages closely with client leadership teams to co-create solutions that are practical and scalable. Known for building strong cross-functional alignment, mentoring teams, and translating strategy into disciplined execution that delivers measurable results.</t>
+  </si>
+  <si>
+    <t>Summary:
+Pramod Harith R is an entrepreneur, growth leader, and go-to-market strategy expert who helps startups and businesses build market fit and scale their offerings. With experience as a venture catalyst, mentor, and speaker, he works with founders and teams to clarify their value proposition and drive sustainable growth.
+Core Expertise:
+Go-to-market strategy, growth marketing, business transformation, startup enablement, market opportunity discovery, demand generation, and founder mentoring. He also brings experience in brand positioning and strategic communications that help early-stage ventures find traction.
+Problem-Solving Approach:
+Pramod takes a founder-centric, practical approach. He focuses on understanding core customer needs, aligning product characteristics with market demand, and building actionable frameworks that teams can execute against. His methods blend strategic insight with hands-on tactics that improve market entry and early adoption success.
+Impactful Projects:
+He leads and facilitates go-to-market bootcamps and startup support programs, including sessions on Market Opportunity Discovery and Go-to-Market Strategy that equip founders with frameworks to assess product-market fit and scale effectively.
+Consultation Style:
+Collaborative and outcome-oriented. Pramod engages with founders and leadership teams through interactive workshops, mentor-led sessions, and tailored strategic guidance. His style emphasizes practical tools, real-world examples, and actionable next steps that help teams move from concept to execution.</t>
+  </si>
+  <si>
+    <t>Summary
+Dhruv Nath is a seasoned startup mentor, angel investor, author, and academic with deep involvement in India’s entrepreneurial ecosystem. With leadership experience across academia and corporate roles, he bridges theory with real-world startup execution. His work focuses on helping founders understand funding realities, sharpen business focus, and build sustainable ventures. Through mentoring, investing, writing, and public discourse, Dhruv consistently simplifies complex startup challenges and offers pragmatic guidance. His impact spans classrooms, boardrooms, and founder communities, making him a trusted voice for early-stage entrepreneurs seeking clarity, discipline, and long-term value creation.
+Key Areas of Expertise
+Angel investing and startup funding dynamics
+Early-stage founder mentoring and ecosystem building
+Startup strategy, focus, and scalability
+Entrepreneurship education and academic leadership
+Authoring practical books on startup funding and growth
+Strategic Contributions
+Guided startups on fundraising readiness and investor expectations
+Contributed thought leadership on startup focus, valuation, and execution
+Invested in and supported multiple early-stage ventures
+Built bridges between academic learning and startup realities
+Enabled founders to make informed strategic and financial decisions
+Mentorship Philosophy
+Strong belief in practical execution over theoretical perfection
+Encourages founders to focus, simplify, and prioritize market realities
+Advocates resilience, adaptability, and disciplined thinking
+Supports founders from diverse backgrounds, regardless of pedigree
+Mentorship centered on honesty, clarity, and long-term sustainability
+Success Stories
+Mentored and influenced hundreds of founders across sectors
+Helped startups refine business models and funding strategies
+Books and insights widely used by entrepreneurs and investors
+Recognized as a credible, no-nonsense mentor in the startup ecosystem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summary:
+Dr. Rakesh Malhotra is an experienced medical professional and healthcare leader with over three decades of clinical practice and healthcare engagement. He serves as a senior physician and director at Neo Hospital and has been associated with multiple healthcare and medical service initiatives in the region. 
+Core Expertise:
+Internal medicine and general physician practice with deep experience in diagnosing and managing a wide range of health conditions. Skilled in internal medicine, infectious disease management, patient diagnosis, health administration, and clinical care coordination. 
+Problem-Solving Approach:
+Dr. Malhotra takes a patient-first approach grounded in meticulous clinical assessment and diagnosis. He integrates evidence-based medicine with empathetic care to tailor treatment plans to individual patient needs, with a strong focus on prevention as well as acute and chronic condition management. 
+Impactful Projects:
+Over 30 years of practice in the Noida and Delhi NCR healthcare ecosystem. He has provided medical consultation and treatment through his long-standing role at Neo Hospital, Sector 50, treating a wide range of internal medicine and general health conditions while building a trusted patient care practice. 
+Consultation Style:
+Calm, thorough, and patient-centric. Known for taking time to understand patient health concerns, explain diagnoses clearly, and involve patients in their care plans. Focuses on building trust and long-term health outcomes through attentive clinical engagement. 
+</t>
+  </si>
+  <si>
+    <t>Summary:
+Simi Mishra is an experienced development sector and communications professional with a strong focus on institutional capacity building, sustainability, and behavior change strategy. She has worked across public policy, sustainable development, and complex systems strengthening initiatives, often engaging with cross-sector partners to design and drive impact-oriented programs.
+Core Expertise:
+Institutional strengthening, behavior change communications, sustainability strategy, systems architecture, public sector engagement, evidence-based policy communication, and multi-stakeholder program leadership. She also works on resource recovery, circular economy, and sustainability discussions in areas such as waste management and environmental inclusion.
+Problem-Solving Approach:
+Simi takes a human-centered approach to complex development challenges. She blends behavior insights with strategic communications to influence systems and stakeholders toward sustainable outcomes. Her methodology emphasizes research-informed interventions and collaborative design with public, private, and civil society actors.
+Impactful Projects:
+She has served as a consultant on global development assignments including work with the World Bank, focusing on behavior change communication and institutional systems improvement. She regularly contributes to thought leadership on sustainability topics such as e-waste and urban mining, advocating for inclusive, equitable approaches that integrate informal sector actors into formal value chains.
+Consultation Style:
+Her style is participatory and strategic. She engages stakeholders through clear frameworks, evidence-based insights, and a focus on building local capacity. Whether working with government bodies, development partners, or industry groups, she emphasizes co-creation, practical implementation, and systems alignment to achieve sustainable impact.</t>
+  </si>
+  <si>
+    <t>Summary Ashish is a seasoned management professional from the telecom and communications industry with over 19 years of diversified experience across techno-managerial roles. He brings deep expertise in OSS/BSS, NMS, Billing Mediation, and large-scale digital transformation programs. With a strong blend of technical depth, business acumen, and entrepreneurial thinking, Ashish has consistently driven complex telecom transformations from strategy to production at global scale. Core Expertise Telecom OSS/BSS, NMS &amp; Billing Mediation Systems Service Assurance &amp; Service Fulfilment Large-scale Program &amp; Delivery Management IT Operations &amp; Managed Services (L1/L2/L3) Architecture, Engineering, Scalability &amp; Resiliency RPA, AI &amp; ML applications for ITSM and Ticket Automation Global Delivery Model &amp; Offshore Program Management Vendor &amp; Stakeholder Management Problem-Solving Approach Ashish adopts a customer-centric and execution-driven approach, combining strong engineering practices with operational excellence. He works closely with customers and internal stakeholders to design scalable, resilient solutions, define clear governance models, and ensure predictable delivery across complex, mission-critical environments. His focus remains on aligning technology outcomes with business value. Impactful Projects Led multi-million-dollar OSS/BSS programs for leading telecom operators across the US, Europe, APAC, and managed services markets. Built and scaled managed services operations and Centers of Excellence for automation using RPA, AI, and ML, improving productivity and service reliability. Played a key role in legacy stack modernization, production operations for 24x7x365 environments, and large-scale system integration programs. Supported pre-sales and business teams by contributing to SOWs, RFP responses, solution design, and executive-level presentations and demos. Consultation Style Ashish follows a collaborative, transparent, and mentorship-driven engagement style. He partners closely with customers, leadership teams, and delivery managers to co-create solutions, build high-performing teams, and enable long-term capability development. Known for strong people leadership, he has successfully managed and mentored 80+ geographically distributed professionals, fostering ownership, accountability, and continuous improvement.</t>
+  </si>
+  <si>
+    <t>Summary:
+Manik Koul is a senior leadership professional with extensive experience in strategy, business transformation, and operational excellence across sectors. He has a strong track record of leading growth initiatives, driving organizational change, and building high-performance teams.
+Core Expertise:
+Strategic planning, business development, operational leadership, performance management, portfolio optimization, and cross-functional collaboration. He has worked across multiple industries with a focus on aligning organizational goals with actionable execution plans to deliver measurable results.
+Problem-Solving Approach:
+Manik applies a structured, insight-driven approach to strategic challenges. He combines analytical rigor with stakeholder alignment to identify root causes, design practical solutions, and mobilize teams toward agreed outcomes. His methodology emphasizes clarity, agility, and continuous learning to navigate complexity and deliver on strategic priorities.
+Impactful Projects:
+He has led transformational programs that span business strategy realignment, operational restructuring, and performance improvement. Through these initiatives, he has helped organizations sharpen their competitive positioning, improve efficiency, and strengthen execution discipline. His work often bridges strategic intent with tangible outcomes across business functions.
+Consultation Style:
+Collaborative, pragmatic, and outcome-focused. Manik engages closely with leaders and teams to co-create strategies that are feasible and impactful. His style emphasizes clear communication, accountability, and a balance between long-term vision and near-term execution, ensuring sustained performance improvement.</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>Marketing: Branding</t>
+  </si>
+  <si>
+    <t>Sales/GTM: Offline Sales Distribution</t>
+  </si>
+  <si>
+    <t>Funding</t>
+  </si>
+  <si>
+    <t>Strategic Planning</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>Enterprise Tech</t>
+  </si>
+  <si>
+    <t>Manufacturing &amp; Manufacturing Tech: Others</t>
+  </si>
+  <si>
+    <t>Media, Arts &amp; Entertainment</t>
+  </si>
+  <si>
+    <t>Climate &amp; Sustainability Tech</t>
   </si>
 </sst>
 </file>
@@ -414,10 +599,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -430,75 +619,178 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/mentors.xlsx
+++ b/mentors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wadhwanifoundation-my.sharepoint.com/personal/meenakshi_singh_wadhwanifoundation_org/Documents/04. Advisors/2026/Test AI Mentor Search/MentorSearchAI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_F25DC773A252ABDACC104819499C5E4E5BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBF2DD90-0550-496F-8F76-FC7CEC9E174C}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="11_F25DC773A252ABDACC104819499C5E4E5BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F19A54A1-1A95-4FE9-857B-3A80D6A4E145}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Linkedin</t>
-  </si>
-  <si>
     <t>Dr. Selva</t>
   </si>
   <si>
@@ -282,6 +279,9 @@
   </si>
   <si>
     <t>Climate &amp; Sustainability Tech</t>
+  </si>
+  <si>
+    <t>LinkedIn</t>
   </si>
 </sst>
 </file>
@@ -620,177 +620,177 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
